--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487400_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487400_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4172</v>
+        <v>9.0663</v>
       </c>
       <c r="E2" t="n">
-        <v>8.852</v>
+        <v>7.5546</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5651</v>
+        <v>1.5117</v>
       </c>
       <c r="G2" t="n">
         <v>6.9163</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7174</v>
+        <v>1.3665</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4013</v>
+        <v>1.1039</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3161</v>
+        <v>0.2626</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7063</v>
+        <v>4.907</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8183</v>
+        <v>3.0723</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8881</v>
+        <v>1.8346</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5102</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.629</v>
+        <v>0.8296</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1764</v>
+        <v>0.4305</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4525</v>
+        <v>0.3991</v>
       </c>
       <c r="V3" t="n">
         <v>2.4332</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6386</v>
+        <v>3.8168</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4349</v>
+        <v>2.6131</v>
       </c>
       <c r="F4" t="n">
         <v>1.2036</v>
@@ -766,10 +766,10 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6052</v>
+        <v>0.7834</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1059</v>
+        <v>0.2841</v>
       </c>
       <c r="U4" t="n">
         <v>0.4993</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8875</v>
+        <v>3.2853</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3922</v>
+        <v>1.6563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4953</v>
+        <v>1.629</v>
       </c>
       <c r="G5" t="n">
         <v>2.5061</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1485</v>
+        <v>0.2492</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2376</v>
+        <v>0.0265</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0891</v>
+        <v>0.2228</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0576</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6336</v>
+        <v>3.1842</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9266</v>
+        <v>3.5307</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.293</v>
+        <v>-0.3465</v>
       </c>
       <c r="G6" t="n">
         <v>4.1623</v>
@@ -922,13 +922,13 @@
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4749</v>
+        <v>1.0254</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3694</v>
+        <v>0.2347</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8442</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-3.3745</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5987</v>
+        <v>1.6999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5977</v>
+        <v>1.5118</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001</v>
+        <v>0.1881</v>
       </c>
       <c r="G7" t="n">
         <v>0.9136</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1183</v>
+        <v>0.2195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0882</v>
+        <v>0.0023</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0301</v>
+        <v>0.2172</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6083</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7419</v>
+        <v>1.234</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4421</v>
+        <v>-0.4673</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2998</v>
+        <v>1.7013</v>
       </c>
       <c r="G8" t="n">
-        <v>0.405</v>
+        <v>-0.3408</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5362</v>
+        <v>-1.1143</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1313</v>
+        <v>0.7734</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6039</v>
+        <v>0.4342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6039</v>
+        <v>-0.3029</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.7371</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.199</v>
+        <v>-0.7751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0677</v>
+        <v>-0.8114</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1313</v>
+        <v>0.0363</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.3191</v>
       </c>
       <c r="T8" t="n">
-        <v>0.504</v>
+        <v>0.1929</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3029</v>
+        <v>0.1262</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6659</v>
+        <v>-0.1152</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6659</v>
+        <v>-0.1152</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7768</v>
+        <v>0.2524</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.89</v>
+        <v>0.0327</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1132</v>
+        <v>0.2196</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3408</v>
+        <v>0.405</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1143</v>
+        <v>0.5362</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7734</v>
+        <v>-0.1313</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4342</v>
+        <v>0.6039</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3029</v>
+        <v>0.6039</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7371</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7751</v>
+        <v>-0.199</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8114</v>
+        <v>-0.0677</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0363</v>
+        <v>-0.1313</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3502</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6917</v>
+        <v>0.3174</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2298</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4619</v>
+        <v>0.2228</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1152</v>
+        <v>-0.6659</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1152</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9165</v>
+        <v>-3.4104</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7779</v>
+        <v>-2.1114</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1386</v>
+        <v>-1.299</v>
       </c>
       <c r="G10" t="n">
         <v>1.8767</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2817</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8475</v>
+        <v>0.514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4342</v>
+        <v>0.2738</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1578</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4701</v>
+        <v>-6.4958</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.651400000000001</v>
+        <v>-7.1693</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1813</v>
+        <v>0.6734</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5015</v>
@@ -1312,13 +1312,13 @@
         <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1057</v>
+        <v>0.8685</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3486</v>
+        <v>0.1335</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2429</v>
+        <v>0.735</v>
       </c>
       <c r="V11" t="n">
         <v>-1.492</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.4604</v>
+        <v>17.5397</v>
       </c>
       <c r="E12" t="n">
-        <v>8.144500000000003</v>
+        <v>10.2235</v>
       </c>
       <c r="F12" t="n">
-        <v>7.315799999999999</v>
+        <v>7.3158</v>
       </c>
       <c r="G12" t="n">
         <v>13.598</v>
@@ -1390,13 +1390,13 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>4.687600000000001</v>
+        <v>6.7664</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9379000000000002</v>
+        <v>3.017100000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>3.749400000000001</v>
+        <v>3.7496</v>
       </c>
       <c r="V12" t="n">
         <v>-5.7627</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.212</v>
+        <v>5.1998</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9617</v>
+        <v>5.3477</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2503</v>
+        <v>-0.1479</v>
       </c>
       <c r="G13" t="n">
         <v>2.1002</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7546</v>
+        <v>-0.2576</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5328000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2217</v>
+        <v>-0.1764</v>
       </c>
       <c r="V13" t="n">
         <v>4.924</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4466</v>
+        <v>1.6826</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9142</v>
+        <v>1.0165</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5324</v>
+        <v>0.6661</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0677</v>
@@ -1546,13 +1546,13 @@
         <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3267</v>
+        <v>-0.0907</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09</v>
+        <v>0.0123</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2367</v>
+        <v>-0.1031</v>
       </c>
       <c r="V14" t="n">
         <v>0.6659</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7083</v>
+        <v>0.7885</v>
       </c>
       <c r="E15" t="n">
         <v>1.2139</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5056</v>
+        <v>-0.4254</v>
       </c>
       <c r="G15" t="n">
         <v>0.7337</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0236</v>
+        <v>0.0566</v>
       </c>
       <c r="V15" t="n">
         <v>0.0576</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3251</v>
+        <v>-1.0993</v>
       </c>
       <c r="E16" t="n">
-        <v>1.254</v>
+        <v>1.0493</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5791</v>
+        <v>-2.1486</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8145</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7479</v>
+        <v>-0.5221</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.18</v>
+        <v>-0.3846</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.1375</v>
       </c>
       <c r="V16" t="n">
         <v>1.2166</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6652</v>
+        <v>-1.4532</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9567</v>
+        <v>-0.8544</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7085</v>
+        <v>-0.5988</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1762</v>
@@ -1780,13 +1780,13 @@
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6054</v>
+        <v>-0.3933</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6534</v>
+        <v>-0.5511</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0481</v>
+        <v>0.1578</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1174</v>
+        <v>-2.6694</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6831</v>
+        <v>-0.4784</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4343</v>
+        <v>-2.1909</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0931</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6914</v>
+        <v>-1.2433</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1286</v>
+        <v>-0.924</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5627</v>
+        <v>-0.3194</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9412</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4989</v>
+        <v>-3.5569</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5309</v>
+        <v>-3.4285</v>
       </c>
       <c r="F19" t="n">
-        <v>0.032</v>
+        <v>-0.1284</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7345</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3139</v>
+        <v>-0.372</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7722</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4583</v>
+        <v>0.2979</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.608</v>
+        <v>-4.2717</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2263</v>
+        <v>-4.3287</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6183</v>
+        <v>0.057</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8121</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1637</v>
+        <v>0.5001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0306</v>
+        <v>-0.1329</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1943</v>
+        <v>0.633</v>
       </c>
       <c r="V20" t="n">
         <v>0.3905</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2054</v>
+        <v>-4.4144</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5252</v>
+        <v>-3.2182</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6801</v>
+        <v>-1.1962</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7836</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5968</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8622</v>
+        <v>-0.5552</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7346</v>
+        <v>-0.2507</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4074</v>
+        <v>-4.9843</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7374</v>
+        <v>-3.6351</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.67</v>
+        <v>-1.3492</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9502</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2406</v>
+        <v>-0.8175</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5058</v>
+        <v>-0.4035</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7348</v>
+        <v>-0.414</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.4605</v>
+        <v>-14.7783</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.315799999999999</v>
+        <v>-7.315900000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.144599999999999</v>
+        <v>-7.4623</v>
       </c>
       <c r="G23" t="n">
         <v>-13.598</v>
@@ -2248,13 +2248,13 @@
         <v>12.73</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.6874</v>
+        <v>-4.005100000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.7494</v>
+        <v>-3.749500000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9380000000000001</v>
+        <v>-0.2557999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>5.762600000000001</v>
